--- a/ig/DM-JANVIER-2025/alignement-nuva-bdpm.xlsx
+++ b/ig/DM-JANVIER-2025/alignement-nuva-bdpm.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.818</t>
+    <t>1.0.825</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05</t>
+    <t>2025-01-06</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -564,6 +564,18 @@
     <t>COMIRNATY OMICRON XBB.1.5 30 microgrammes/dose, dispersion injectable. Vaccin à ARNm (à nucléoside modifié) contre la COVID-19</t>
   </si>
   <si>
+    <t>VAC0620</t>
+  </si>
+  <si>
+    <t>IXCHIQ</t>
+  </si>
+  <si>
+    <t>3400930296448</t>
+  </si>
+  <si>
+    <t>IXCHIQ, poudre et solvant pour solution injectable. Vaccin contre le chikungunya (vivant) 1 flacon unidose en verre + 1 seringue préremplie en verre de 0,5 mL</t>
+  </si>
+  <si>
     <t>VAC0050</t>
   </si>
   <si>
@@ -1194,18 +1206,6 @@
     <t>SHINGRIX, poudre et suspension pour suspension injectable. Vaccin zona (recombinant, avec adjuvant) 1 flacon en verre de 50 microgrammes de poudre  - 1 flacon en verre de 0,5 ml de suspension</t>
   </si>
   <si>
-    <t>VAC0010</t>
-  </si>
-  <si>
-    <t>HBVAXPRO 40 µg</t>
-  </si>
-  <si>
-    <t>64757607</t>
-  </si>
-  <si>
-    <t>HBVAXPRO 40 microgrammes, suspension injectable. Vaccin de l'hépatite B (ADNr)</t>
-  </si>
-  <si>
     <t>VAC0562</t>
   </si>
   <si>
@@ -1755,13 +1755,13 @@
     <t>65802140</t>
   </si>
   <si>
-    <t>TRUMENBA, suspension injectable en seringue préremplie</t>
+    <t>TRUMENBA, suspension injectable en seringue préremplie. Vaccin méningococcique groupe B (recombinant, adsorbé)</t>
   </si>
   <si>
     <t>3400930096376</t>
   </si>
   <si>
-    <t>TRUMENBA, suspension injectable en seringue préremplie 1 seringue préremplie en verre de 0,5 ml avec aiguille</t>
+    <t>TRUMENBA, suspension injectable en seringue préremplie. Vaccin méningococcique groupe B (recombinant, adsorbé) 1 seringue préremplie en verre de 0,5 ml avec aiguille</t>
   </si>
 </sst>
 </file>
@@ -2963,27 +2963,27 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C56" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>34</v>
@@ -2997,27 +2997,27 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>34</v>
@@ -3031,27 +3031,27 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C60" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C61" t="s" s="2">
         <v>34</v>
@@ -3065,27 +3065,27 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>34</v>
@@ -3116,61 +3116,61 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C65" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C66" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C67" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>34</v>
@@ -3184,27 +3184,27 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>34</v>
@@ -3218,27 +3218,27 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>34</v>
@@ -3252,44 +3252,44 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>34</v>
@@ -3303,61 +3303,61 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C78" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C79" t="s" s="2">
         <v>34</v>
@@ -3388,27 +3388,27 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C82" t="s" s="2">
         <v>34</v>
@@ -3422,27 +3422,27 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C83" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C84" t="s" s="2">
         <v>34</v>
@@ -3456,27 +3456,27 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C86" t="s" s="2">
         <v>34</v>
@@ -3490,44 +3490,44 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C87" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C88" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C89" t="s" s="2">
         <v>34</v>
@@ -3541,27 +3541,27 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C91" t="s" s="2">
         <v>34</v>
@@ -3575,27 +3575,27 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C92" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>34</v>
@@ -3609,27 +3609,27 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C94" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>34</v>
@@ -3643,27 +3643,27 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C96" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C97" t="s" s="2">
         <v>34</v>
@@ -3677,27 +3677,27 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>34</v>
@@ -3711,27 +3711,27 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C101" t="s" s="2">
         <v>34</v>
@@ -3745,27 +3745,27 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>34</v>
@@ -3779,27 +3779,27 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C104" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C105" t="s" s="2">
         <v>34</v>
@@ -3813,44 +3813,44 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C107" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C108" t="s" s="2">
         <v>34</v>
@@ -3864,27 +3864,27 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C109" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C110" t="s" s="2">
         <v>34</v>
@@ -3898,44 +3898,44 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C111" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C112" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C113" t="s" s="2">
         <v>34</v>
@@ -3949,27 +3949,27 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C114" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C115" t="s" s="2">
         <v>34</v>
@@ -3983,27 +3983,27 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C116" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D116" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C117" t="s" s="2">
         <v>34</v>
@@ -4017,27 +4017,27 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C118" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E118" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C119" t="s" s="2">
         <v>34</v>
@@ -4051,27 +4051,27 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C120" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D120" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C121" t="s" s="2">
         <v>34</v>
@@ -4085,27 +4085,27 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>34</v>
@@ -4119,27 +4119,27 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C124" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E124" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>34</v>
@@ -4153,27 +4153,27 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C126" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E126" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C127" t="s" s="2">
         <v>34</v>
